--- a/2.RCM/PLC_Sales_RCM.xlsx
+++ b/2.RCM/PLC_Sales_RCM.xlsx
@@ -562,6 +562,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1357,7 +1358,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>価格マスタの新規登録・変更申請は、営業担当がワークフロー（S04）で起票し、営業本部長（E0021）の承認を得る。経理部（E0014）が月次で変更履歴をレビューする。</t>
+          <t>価格マスタの新規登録・変更申請は、営業担当が稟議ワークフロー（S04）で事前に起票し、営業本部長（E0021）の承認を得る。承認後、営業担当がSAP VK12でマスタ変更を実行する。経理部（E0014）が月次でSAP VK12変更履歴と稟議承認記録を突合レビューする。</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">

--- a/2.RCM/PLC_Sales_RCM.xlsx
+++ b/2.RCM/PLC_Sales_RCM.xlsx
@@ -558,7 +558,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評価対象: 株式会社テクノプレシジョン 親会社  /  評価期間: FY2025 (2025/4/1 - 2026/3/31)  /  作成日: 2026/04/10  /  作成者: 内部監査室</t>
+          <t>評価対象: デモA株式会社 親会社  /  評価期間: FY2025 (2025/4/1 - 2026/3/31)  /  作成日: 2026/04/10  /  作成者: 内部監査室</t>
         </is>
       </c>
     </row>
@@ -1461,6 +1461,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
